--- a/knowledge/questions/Claude code practice test.xlsx
+++ b/knowledge/questions/Claude code practice test.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epam-my.sharepoint.com/personal/meruyert_sikym_epam_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeruyertSikym\Documents\Claude code agents\knowledge\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{59E906FB-3DC7-498F-BD73-F958104397F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68C96B50-AF41-4603-9E08-C388C47B42B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8392689-6C08-48AD-A100-9BAC45C4BD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9D219C89-A46C-4E66-8F86-53BE37AB4D20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$64</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -1117,6 +1120,336 @@
 The asynchronous model prevents executing tools mid-request and returning results for Claude to continue analysis.
 D
 Batch processing lacks request correlation identifiers for matching outputs to input requests.</t>
+  </si>
+  <si>
+    <t>Production logs show that for simple requests like "refund order #1234", your agent succeeds in 3-4 tool calls with 91% resolution rate. However, for complex requests like "I've been charged twice, my discount didn't apply, and I want to cancel", the agent averages 12+ tool calls with only 54% resolution—often investigating concerns sequentially and gathering redundant customer data for each one. What's the most effective change to improve complex request handling?</t>
+  </si>
+  <si>
+    <t>A
+Add explicit verification gates between steps requiring the agent to checkpoint after resolving each concern before moving to the next.
+B
+Add few-shot examples demonstrating ideal tool call sequences for various multi-part billing scenarios to your system prompt.
+C
+Reduce the number of available tools by consolidating get_customer, lookup_order, and billing-related lookups into a single investigate_issue tool.
+D
+Decompose the request into distinct concerns, then investigate each in parallel using shared customer context before synthesizing a resolution.</t>
+  </si>
+  <si>
+    <t>D
+Decompose the request into distinct concerns, then investigate each in parallel using shared customer context before synthesizing a resolution.</t>
+  </si>
+  <si>
+    <t>Decomposing the request into distinct concerns and investigating them in parallel with shared customer context directly addresses both core issues: it eliminates redundant data fetching by reusing context across concerns and reduces total tool calls by parallelizing investigations before synthesizing a unified resolution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+B
+Add few-shot examples demonstrating ideal tool call sequences for various multi-part billing scenarios to your system prompt.</t>
+  </si>
+  <si>
+    <t>While few-shot examples might marginally improve tool call sequences for known scenarios, they don't systematically solve the structural problems of redundant context gathering or sequential investigation, and they won't generalize well to novel multi-part request combinations.</t>
+  </si>
+  <si>
+    <t>Production logs reveal a consistent pattern: when customers include "account" in messages (e.g., "I want to check my account for the order I placed yesterday"), the agent calls get_customer first 78% of the time. When customers phrase similar requests without "account" (e.g., "I want to check on the order I placed yesterday"), it calls lookup_order first 93% of the time. The tool descriptions are well-written and unambiguous. What is the most likely root cause of this discrepancy?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+The system prompt contains keyword-sensitive instructions that steer behavior based on terms like "account," creating unintended tool selection patterns
+B
+The tool descriptions need additional negative examples specifying when NOT to use each tool to prevent this keyword-triggered confusion
+C
+The model requires more training data on multi-concept messages and should be fine-tuned on examples that include both account and order language
+D
+The model's base training creates associations between "account" terminology and customer-related operations that override the tool descriptions</t>
+  </si>
+  <si>
+    <t>A
+The system prompt contains keyword-sensitive instructions that steer behavior based on terms like "account," creating unintended tool selection patterns</t>
+  </si>
+  <si>
+    <t>This is the most likely root cause because the systematic, keyword-triggered pattern (78% vs 93%) strongly suggests explicit routing logic in the system prompt that reacts to the word "account" and directs the agent toward customer-related tools. Since the tool descriptions are already well-written and unambiguous, the discrepancy points to prompt-level instructions creating unintended behavioral steering.</t>
+  </si>
+  <si>
+    <t>In testing, you notice the agent frequently calls get_customer when users ask about order status, even though lookup_order would be more appropriate. What should you examine first to address this issue?</t>
+  </si>
+  <si>
+    <t>A
+Add few-shot examples covering every possible order-related query pattern to the system prompt
+B
+Reduce the number of tools available to the agent to simplify selection
+C
+Implement a pre-processing classifier that detects order queries and routes directly to lookup_order
+D
+Review tool descriptions to ensure they clearly distinguish each tool's purpose</t>
+  </si>
+  <si>
+    <t>D
+Review tool descriptions to ensure they clearly distinguish each tool's purpose</t>
+  </si>
+  <si>
+    <t>Tool descriptions are the primary input the model uses to decide which tool to call. When an agent consistently selects the wrong tool, the first diagnostic step is to examine whether the tool descriptions clearly distinguish each tool's purpose and specify when each should be used.</t>
+  </si>
+  <si>
+    <t>Your agent achieves 55% first-contact resolution, well below the 80% target. Logs show it escalates straightforward cases (standard damage replacements with photo evidence) while attempting to autonomously handle complex situations requiring policy exceptions. What's the most effective way to improve escalation calibration?</t>
+  </si>
+  <si>
+    <t>A
+Implement sentiment analysis to detect customer frustration levels and automatically escalate when negative sentiment exceeds a threshold.
+B
+Deploy a separate classifier model trained on historical tickets to predict which requests need escalation before the main agent begins processing.
+C
+Add explicit escalation criteria to your system prompt with few-shot examples demonstrating when to escalate versus resolve autonomously.
+D
+Have the agent self-report a confidence score (1-10) before each response and automatically route requests to humans when confidence falls below a threshold.</t>
+  </si>
+  <si>
+    <t>C
+Add explicit escalation criteria to your system prompt with few-shot examples demonstrating when to escalate versus resolve autonomously.</t>
+  </si>
+  <si>
+    <t>Adding explicit escalation criteria with few-shot examples directly addresses the root cause—unclear decision boundaries between straightforward and complex cases. This is the most proportionate and effective first intervention, as it teaches the agent precisely when to escalate versus resolve autonomously without requiring additional infrastructure.</t>
+  </si>
+  <si>
+    <t>Production logs show the agent sometimes selects get_customer when lookup_order would be more appropriate, particularly for ambiguous requests like "I need help with my recent purchase." You decide to add few-shot examples to your system prompt to improve tool selection. Which approach will most effectively address this issue?</t>
+  </si>
+  <si>
+    <t>A
+Add 4-6 examples targeting ambiguous scenarios, each showing reasoning for why one tool was chosen over plausible alternatives.
+B
+Add examples grouped by tool—all get_customer scenarios together, then all lookup_order scenarios.
+C
+Add 10-15 examples of clear, unambiguous requests that demonstrate correct tool selection for each tool's typical use cases.
+D
+Add explicit "use when" and "do not use when" guidelines in each tool's description covering the ambiguous cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Add 4-6 examples targeting ambiguous scenarios, each showing reasoning for why one tool was chosen over plausible alternatives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Targeting few-shot examples at the specific ambiguous scenarios where errors occur, with explicit reasoning about why one tool is preferred over another, directly teaches the model the comparative decision-making process it needs for edge cases. This approach is the most effective because worked examples demonstrating reasoning are better than declarative rules for nuanced tool selection.
+</t>
+  </si>
+  <si>
+    <t>A
+Implement a preprocessing layer that uses a separate model call to decompose multi-concern messages into individual requests, process each independently, then combine the results.
+B
+Add few-shot examples to your prompt demonstrating the correct reasoning and tool sequence for multi-concern requests.
+C
+Consolidate related tools into fewer, more general-purpose tools.
+D
+Implement response validation that detects incomplete responses and automatically re-prompts the agent to address any missed concerns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your agent handles single-concern requests with 94% accuracy (e.g., "I need a refund for order #1234"). However, when customers include multiple concerns in one message (e.g., "I need a refund for order #1234 and also want to update my shipping address for order #5678"), tool selection accuracy drops to 58%. The agent typically addresses only one concern or mixes up parameters between requests. What's the most effective approach to improve reliability for multi-concern requests?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Implement a preprocessing layer that uses a separate model call to decompose multi-concern messages into individual requests, process each independently, then combine the results.</t>
+  </si>
+  <si>
+    <t>B
+Add few-shot examples to your prompt demonstrating the correct reasoning and tool sequence for multi-concern requests.</t>
+  </si>
+  <si>
+    <t>Adding few-shot examples demonstrating correct reasoning and tool sequencing for multi-concern requests is the most effective approach because the agent already handles individual concerns well at 94% accuracy—it simply needs pattern guidance for handling multiple concerns in one message. This is a low-cost, proven technique that directly addresses the root cause of the agent failing to decompose and properly route parameters across multiple requests.</t>
+  </si>
+  <si>
+    <t>Using a separate model call to decompose multi-concern messages adds unnecessary latency, complexity, and cost when the agent already demonstrates strong single-concern understanding. This over-engineers the solution when simpler prompt-level guidance can address the pattern recognition gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production data shows that in 12% of cases, your agent skips get_customer entirely and calls lookup_order using only the customer's stated name, occasionally leading to misidentified accounts and incorrect refunds. What change would most effectively address this reliability issue?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Implement a routing classifier that analyzes each request and enables only the subset of tools appropriate for that request type.
+B
+Add a programmatic prerequisite that blocks lookup_order and process_refund calls until get_customer has returned a verified customer ID.
+C
+Add few-shot examples showing the agent always calling get_customer first, even when customers volunteer order details.
+D
+Enhance the system prompt to state that customer verification via get_customer is mandatory before any order operations.</t>
+  </si>
+  <si>
+    <t>B
+Add a programmatic prerequisite that blocks lookup_order and process_refund calls until get_customer has returned a verified customer ID.</t>
+  </si>
+  <si>
+    <t>Adding a programmatic prerequisite that blocks downstream tools until `get_customer` returns a verified customer ID provides a deterministic guarantee that the required sequence is followed. This is the most effective approach because it removes the possibility of the agent skipping verification, regardless of LLM behavior.</t>
+  </si>
+  <si>
+    <t>Production logs reveal that the agent misinterprets data from your MCP tools: Unix timestamps from get_customer, ISO 8601 dates from lookup_order, and numeric status codes (1=pending, 2=shipped). Some tools are third-party MCP servers you cannot modify. What's the most maintainable approach to normalize data formats?</t>
+  </si>
+  <si>
+    <t>A
+Modify tools you control to return human-readable formats; create wrapper tools for third-party tools
+B
+Create a normalize_data tool that the agent calls after each data retrieval to transform values
+C
+Add detailed format documentation to your system prompt explaining each tool's data conventions
+D
+Use a PostToolUse hook to intercept tool results and apply formatting transformations before agent processing</t>
+  </si>
+  <si>
+    <t>D
+Use a PostToolUse hook to intercept tool results and apply formatting transformations before agent processing</t>
+  </si>
+  <si>
+    <t>Using a PostToolUse hook provides a centralized, deterministic point to intercept and normalize all tool outputs—including those from third-party MCP servers—before the agent processes them. This is the most maintainable approach because it applies transformations uniformly via code rather than relying on LLM interpretation or agent behavior.</t>
+  </si>
+  <si>
+    <t>You're implementing the agentic loop for your support agent. After each API call to Claude, you need to determine whether to continue the loop (execute the requested tools and call Claude again) or stop (present the final response to the customer). What determines this decision?</t>
+  </si>
+  <si>
+    <t>A
+Parse Claude's response text for phrases like "I've completed" or "Is there anything else?"—these natural language signals indicate the task is finished.
+B
+Set a maximum iteration count (e.g., 10 calls) and stop when reached, regardless of whether Claude indicates more work is needed.
+C
+Check the stop_reason field in Claude's response—continue when it equals "tool_use" and stop when it equals "end_turn".
+D
+Check whether the response includes any assistant text content—if Claude generated explanatory text, the loop should end.</t>
+  </si>
+  <si>
+    <t>C
+Check the stop_reason field in Claude's response—continue when it equals "tool_use" and stop when it equals "end_turn".</t>
+  </si>
+  <si>
+    <t>This is correct. The `stop_reason` field is Claude's explicit, structured signal for loop control: `"tool_use"` indicates Claude wants to execute a tool and receive the results back, while `"end_turn"` indicates Claude has completed its response and the loop should terminate.</t>
+  </si>
+  <si>
+    <t>Your support agent uses progressive summarization—when context reaches 70% capacity, older turns are summarized while recent ones remain verbatim. Production logs reveal a pattern: customers reference specific amounts ("the 15% discount I mentioned"), but the agent responds with incorrect values. Investigation shows these details were stated 20+ turns ago and got condensed into vague summaries like "discussed promotional pricing." What's the most effective fix?</t>
+  </si>
+  <si>
+    <t>A
+Revise the summarization prompt to explicitly preserve all numerical values, percentages, dates, and customer-stated expectations verbatim.
+B
+Store full conversation history externally and implement retrieval to search it when the agent detects reference phrases like "as I mentioned."
+C
+Extract transactional facts (amounts, dates, order numbers) into a persistent "case facts" block included in each prompt, outside the summarized history.
+D
+Increase the summarization threshold from 70% to 85% capacity so conversations have more room before summarization triggers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+C
+Extract transactional facts (amounts, dates, order numbers) into a persistent "case facts" block included in each prompt, outside the summarized history.</t>
+  </si>
+  <si>
+    <t>Extracting transactional facts (amounts, dates, order numbers) into a persistent "case facts" block addresses the root cause: summarization is inherently lossy for precise details. By preserving critical information in a structured block outside the summarized history, these facts remain reliably available in every prompt regardless of how many turns are summarized.</t>
+  </si>
+  <si>
+    <t>Your get_customer tool returns all matches when searching by name. Claude currently picks the customer with the most recent order when multiple results are returned, but production data shows this causes 15% of multi-match cases to proceed with the wrong customer account. How should you address this?</t>
+  </si>
+  <si>
+    <t>A
+Modify get_customer to return only the single most likely match based on a ranking algorithm, simplifying Claude's decision by eliminating ambiguous results.
+B
+Implement a confidence scoring system that proceeds automatically above 85% confidence and prompts for clarification below that threshold.
+C
+Instruct Claude to ask for an additional identifier (email, phone, or order number) when get_customer returns multiple matches, before taking any customer-specific action.
+D
+Add few-shot examples showing Claude how to use conversational context (products mentioned, dates referenced) to infer the correct customer without requiring clarification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+C
+Instruct Claude to ask for an additional identifier (email, phone, or order number) when get_customer returns multiple matches, before taking any customer-specific action.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asking the user for an additional identifier (such as email, phone, or order number) is the most reliable way to disambiguate multiple matches, since the user has definitive knowledge of their own identity. One extra conversational turn is a small cost to eliminate the 15% error rate caused by incorrect customer selection.
+</t>
+  </si>
+  <si>
+    <t>Production metrics show that when your agent resolves complex cases involving billing disputes or multi-order returns, customer satisfaction scores are 15% lower than for simple cases—even when the resolution is technically correct. Root cause analysis reveals the agent provides accurate resolutions but inconsistently explains the reasoning: sometimes omitting relevant policy details, other times missing timeline information or next steps. The specific context gaps vary by case. You want to improve resolution quality without adding human review overhead. Which approach is most effective?</t>
+  </si>
+  <si>
+    <t>A
+Add a self-critique step where the agent evaluates its draft response for completeness—ensuring it addresses the customer's concern, includes relevant context, and anticipates follow-up questions.
+B
+Add a confirmation step where the agent asks "Does this fully address your concern?" before closing, letting customers request additional information if needed.
+C
+Implement few-shot examples in the system prompt showing complete resolution explanations for five common complex case types, demonstrating how to include policy context, timelines, and next steps.
+D
+Increase the model tier from Haiku to Sonnet for complex cases, routing based on detected case complexity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Add a self-critique step where the agent evaluates its draft response for completeness—ensuring it addresses the customer's concern, includes relevant context, and anticipates follow-up questions.</t>
+  </si>
+  <si>
+    <t>A self-critique step (evaluator-optimizer pattern) directly addresses the root cause of inconsistent explanation completeness by having the agent evaluate its own draft against specific criteria—such as policy context, timelines, and next steps—before presenting it. This catches case-specific gaps that vary across different complex scenarios without requiring human review.</t>
+  </si>
+  <si>
+    <t>Production metrics show your agent averages 4+ API round-trips per resolution. Analysis reveals Claude frequently requests get_customer and lookup_order in separate sequential turns even when both are needed upfront. What's the most effective way to reduce round-trips?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Increase max_tokens to give Claude more space to plan ahead and naturally batch its tool requests.
+B
+Prompt Claude to batch tool requests per turn, and return all tool results together before the next API call.
+C
+Implement speculative execution that automatically calls likely-needed tools alongside any requested tool, returning all results regardless of what was requested.
+D
+Create composite tools like get_customer_with_orders that bundle common lookup combinations into single calls.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+B
+Prompt Claude to batch tool requests per turn, and return all tool results together before the next API call.</t>
+  </si>
+  <si>
+    <t>Prompting Claude to batch related tool requests in a single turn, and returning all results together before the next API call, leverages Claude's native ability to request multiple tools simultaneously. This is the most effective approach because it directly addresses the sequential calling pattern with minimal architectural changes.</t>
+  </si>
+  <si>
+    <t>After calling get_customer and lookup_order, the agent has retrieved all available system data but faces uncertainty. Which situation represents the most appropriate trigger for calling escalate_to_human?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+The customer claims they never received their order, but tracking shows it was delivered and signed for at their address three days ago. The agent should escalate because presenting contradictory evidence might damage the customer relationship.
+B
+The customer requests a price match against a competitor. Your policies allow adjustments for price drops on your own site within 14 days but are silent on competitor pricing. The agent should escalate for policy interpretation.
+C
+The customer wants to cancel an order that shipped yesterday, with delivery scheduled for tomorrow. The agent should escalate because the customer might change their mind once they receive the package.
+D
+The customer's message mentions both a billing question and a product return. The agent should escalate so a human can coordinate handling both issues in a single interaction.</t>
+  </si>
+  <si>
+    <t>B
+The customer requests a price match against a competitor. Your policies allow adjustments for price drops on your own site within 14 days but are silent on competitor pricing. The agent should escalate for policy interpretation.</t>
+  </si>
+  <si>
+    <t>This represents a genuine policy gap where the company's guidelines cover own-site price drops but are silent on competitor price matching, meaning the agent cannot fabricate a policy and must escalate for human judgment on how to interpret or extend existing rules.</t>
+  </si>
+  <si>
+    <t>Production logs show the agent frequently calls get_customer when users ask about orders (e.g., "check my order #12345"), instead of calling lookup_order. Both tools have minimal descriptions ("Retrieves customer information" / "Retrieves order details") and accept similar identifier formats. What's the most effective first step to improve tool selection reliability?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A
+Consolidate both tools into a single lookup_entity tool that accepts any identifier and internally determines which backend to query.
+B
+Expand each tool's description to include input formats it handles, example queries, edge cases, and boundaries explaining when to use it versus similar tools.
+C
+Implement a routing layer that parses user input before each turn and pre-selects the appropriate tool based on detected keywords and identifier patterns.
+D
+Add few-shot examples to the system prompt demonstrating correct tool selection patterns, with 5-8 examples showing order-related queries routing to lookup_order.</t>
+  </si>
+  <si>
+    <t>B
+Expand each tool's description to include input formats it handles, example queries, edge cases, and boundaries explaining when to use it versus similar tools.</t>
+  </si>
+  <si>
+    <t>Expanding tool descriptions to include input formats, example queries, edge cases, and boundaries directly addresses the root cause—minimal descriptions that leave the LLM unable to distinguish between similar tools. This is a low-effort, high-leverage first step that improves the primary mechanism LLMs use for tool selection.</t>
   </si>
 </sst>
 </file>
@@ -1491,16 +1824,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32476A57-6E20-4EEC-BDFE-13EC5BDDDAC1}">
-  <dimension ref="A1:L59"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" customWidth="1"/>
     <col min="2" max="2" width="45.6640625" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="34.21875" customWidth="1"/>
-    <col min="5" max="5" width="26.5546875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" customWidth="1"/>
     <col min="8" max="8" width="24.88671875" customWidth="1"/>
     <col min="9" max="9" width="22.33203125" customWidth="1"/>
     <col min="10" max="10" width="21.6640625" customWidth="1"/>
@@ -2761,11 +3097,13 @@
         <v>208</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="1"/>
+      <c r="B47" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="C47" s="1" t="s">
         <v>209</v>
       </c>
@@ -2775,169 +3113,425 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="H47" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+    <row r="49" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
+      <c r="H49" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+    <row r="50" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
+      <c r="H50" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+    <row r="51" spans="1:12" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
+      <c r="H51" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+    <row r="52" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
+      <c r="H53" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+    <row r="54" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="H54" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+    <row r="55" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+    <row r="56" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+    <row r="57" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
+      <c r="H57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+    <row r="58" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="H58" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+    <row r="59" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="H59" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
     </row>
+    <row r="60" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="42" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>